--- a/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -15,12 +15,13 @@
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
     <sheet name="Include #6" r:id="rId10" sheetId="8"/>
     <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -67,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17</t>
+    <t>2026-05-08</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -385,6 +386,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>

--- a/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define Alpha-ID codes allowed for diagnosis coding in the MII Diagnosis module.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -363,22 +366,24 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -397,28 +402,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -437,28 +442,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -477,28 +482,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -517,28 +522,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -557,28 +562,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -597,28 +602,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -637,28 +642,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -677,28 +682,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -717,28 +722,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
